--- a/tests/realSuite/Atletica Rovereto/input.xlsx
+++ b/tests/realSuite/Atletica Rovereto/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,91 +451,91 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC ARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fermata bus – Via Filzi, Aldeno</t>
+          <t>SSPG – Via Caproni, Loc. Prabi, Arco</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IC ALDENO-MATTARELLO</t>
+          <t>IC AVIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scuola – Via Torre Franca 1, Mattarello</t>
+          <t>Viale Degasperi 69, Avio</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC ARCO</t>
+          <t>IC BORGO VALSUGANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SSPG – Via Caproni, Loc. Prabi, Arco</t>
+          <t>SSPG - Via A. Spagolla 1, Borgo Valsugana</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC AVIO</t>
+          <t>IC CAVALESE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Viale Degasperi 69, Avio</t>
+          <t>Piazza Verdi 6, Cavalese</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC BORGO VALSUGANA</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SSPG - Via A. Spagolla 1, Borgo Valsugana</t>
+          <t>SSPG – Loc. Scancio 69, Segonzano</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC CAVALESE</t>
+          <t>IC CEMBRA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Piazza Verdi 6, Cavalese</t>
+          <t>SSPG – Via Grec 2, Giovo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -546,146 +546,146 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SSPG – Loc. Scancio 69, Segonzano</t>
+          <t>SSPG – Via Negritelle 1, Cembra</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC DRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SSPG – Via Grec 2, Giovo</t>
+          <t>SSPG – Via S. Antonio 174, Dro</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC CEMBRA</t>
+          <t>IC FOLGARIA-LAVARONE-LUSERNA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SSPG – Via Negritelle 1, Cembra</t>
+          <t>Fermata bus Palaghiaccio, Folgaria</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC DRO</t>
+          <t>IC FOLGARIA-LAVARONE-LUSERNA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SSPG – Via S. Antonio 174, Dro</t>
+          <t>Frazione Gionghi 107/6, Lavarone</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC FOLGARIA-LAVARONE-LUSERNA</t>
+          <t>IC LADINO DI FASSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fermata bus Palaghiaccio, Folgaria</t>
+          <t>Str. Dolomites – San Giovanni di Fassa</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC FOLGARIA-LAVARONE-LUSERNA</t>
+          <t>IC LAVIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Frazione Gionghi 107/6, Lavarone</t>
+          <t>SSPG – Via Sette 13/a, Lavis</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC LADINO DI FASSA</t>
+          <t>IC LEVICO TERME</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Str. Dolomites – San Giovanni di Fassa</t>
+          <t>SSPG - Via della Pace 5, Levico Terme</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC LAVIS</t>
+          <t>IC MEZZOCORONA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SSPG – Via Sette 13/a, Lavis</t>
+          <t>Via Fornai 1, Mezzocorona</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC LEVICO TERME</t>
+          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SSPG - Via della Pace 5, Levico Terme</t>
+          <t>Piazza San Vito 1, Andalo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC MEZZOCORONA</t>
+          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Via Fornai 1, Mezzocorona</t>
+          <t>Via Trento, Spormaggiore</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -696,52 +696,52 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Piazza San Vito 1, Andalo</t>
+          <t>Via degli Alpini 17, Mezzolombardo</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
+          <t>IC PERGINE 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Via Trento, Spormaggiore</t>
+          <t>SSPG – Via Caduti 39, Pergine Valsugana</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IC MEZZOLOMBARDO-PAGANELLA</t>
+          <t>IC PERGINE 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Via degli Alpini 17, Mezzolombardo</t>
+          <t>SSPG – Via Dante 276, Pergine Valsugana</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IC PERGINE 1</t>
+          <t>IC RIVA 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SSPG – Via Caduti 39, Pergine Valsugana</t>
+          <t>Centro sportivo Malossini – Via Ginestre, Riva del Garda</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -751,82 +751,82 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IC PERGINE 2</t>
+          <t>IC TIONE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SSPG – Via Dante 276, Pergine Valsugana</t>
+          <t>SSPG – Via Circonvallazione 44, Tione</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IC RIVA 2</t>
+          <t>IC TRENTO 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Centro sportivo Malossini – Via Ginestre, Riva del Garda</t>
+          <t>SSPG – Via Znojmo 24, Povo/Trento</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IC TIONE</t>
+          <t>IC TRENTO 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SSPG – Via Circonvallazione 44, Tione</t>
+          <t>SSPG – Via Ponte Alto 2/1, Cognola/Trento</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IC TRENTO 1</t>
+          <t>IC TRENTO 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SSPG – Via Znojmo 24, Povo/Trento</t>
+          <t>Park ex Italcementi – fermata bus, Trento</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IC TRENTO 2</t>
+          <t>IC TRENTO 4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SSPG – Via Ponte Alto 2/1, Cognola/Trento</t>
+          <t>Park Chiesa Sacro Cuore – Viale Verona, Trento</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IC TRENTO 3</t>
+          <t>IC TRENTO 5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -841,37 +841,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IC TRENTO 4</t>
+          <t>IC TRENTO 6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Park Chiesa Sacro Cuore – Viale Verona, Trento</t>
+          <t>Park ex Italcementi – fermata bus, Trento</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IC TRENTO 5</t>
+          <t>IC TRENTO 7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Park ex Italcementi – fermata bus, Trento</t>
+          <t>SSPG – Via Quattro Novembre 35/1, Gardolo/Trento</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IC TRENTO 6</t>
+          <t>IC TRENTO ARCIVESCOVILE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -880,96 +880,66 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IC TRENTO 7</t>
+          <t>IC VALLE DI LEDRO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SSPG – Via Quattro Novembre 35/1, Gardolo/Trento</t>
+          <t>Via Falcone e Borsellino, Bezzecca</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IC TRENTO ARCIVESCOVILE</t>
+          <t>IC VEZZANO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Park ex Italcementi – fermata bus, Trento</t>
+          <t>Via Roma, Vezzano</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IC VALLE DI LEDRO</t>
+          <t>IC VEZZANO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Via Falcone e Borsellino, Bezzecca</t>
+          <t>Via XXV Aprile 7, Cavedine</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IC VEZZANO</t>
+          <t>IC VIGOLO VATTARO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Via Roma, Vezzano</t>
+          <t>Via Garibaldi - fermata bus, Vigolo Vattaro</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>IC VEZZANO</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Via XXV Aprile 7, Cavedine</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>IC VIGOLO VATTARO</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Via Garibaldi - fermata bus, Vigolo Vattaro</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
         <v>27</v>
       </c>
     </row>
